--- a/data/Employee_Directory.xlsx
+++ b/data/Employee_Directory.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kate\OneDrive\Documents\GRC_Risk_Assessment\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kate\OneDrive\Documents\GRC_Risk_Assessment\C3-GRC\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{671815AA-EC51-4DBD-BE1C-BED2D822092A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -1082,7 +1082,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="57" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="68.400000000000006" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>100</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="45.6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="57" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>94</v>
       </c>
@@ -1188,7 +1188,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="45.6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" ht="57" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>88</v>
       </c>
